--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507778.9782748962</v>
+        <v>507779</v>
       </c>
       <c r="R2" t="n">
-        <v>6343047.8613535</v>
+        <v>6343048</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507778.9782748962</v>
+        <v>507779</v>
       </c>
       <c r="R3" t="n">
-        <v>6343047.8613535</v>
+        <v>6343048</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51489-2024 artfynd.xlsx
+++ b/artfynd/A 51489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983314</v>
       </c>
       <c r="B2" t="n">
-        <v>109264</v>
+        <v>109814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74154396</v>
       </c>
       <c r="B3" t="n">
-        <v>104137</v>
+        <v>104627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
